--- a/data/b2_centro/B2 Centro 10-2025.xlsx
+++ b/data/b2_centro/B2 Centro 10-2025.xlsx
@@ -4945,7 +4945,7 @@
         </is>
       </c>
       <c r="D2" s="16" t="n">
-        <v>77935.75</v>
+        <v>78432.98</v>
       </c>
     </row>
     <row r="3">
@@ -4954,52 +4954,52 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Outras despesas</t>
+          <t>Taxas de cartão</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Tarifas bancárias</t>
+          <t>Taxas das maquininhas (semana)</t>
         </is>
       </c>
       <c r="D3" s="17" t="n">
-        <v>1769.61</v>
+        <v>3977.01</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="7" t="n">
-        <v>45935</v>
+        <v>45937</v>
       </c>
       <c r="B4" s="8" t="inlineStr">
         <is>
-          <t>Taxas de cartão</t>
+          <t>Outras despesas</t>
         </is>
       </c>
       <c r="C4" s="8" t="inlineStr">
         <is>
-          <t>Taxas das maquininhas (semana)</t>
+          <t>Material de limpeza e escritório</t>
         </is>
       </c>
       <c r="D4" s="16" t="n">
-        <v>3710.2</v>
+        <v>2338.25</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="12" t="n">
-        <v>45936</v>
+        <v>45940</v>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Outras despesas</t>
+          <t>Aluguel</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Material de limpeza e escritório</t>
+          <t>Aluguel do imóvel</t>
         </is>
       </c>
       <c r="D5" s="17" t="n">
-        <v>1756.52</v>
+        <v>38000</v>
       </c>
     </row>
     <row r="6">
@@ -5008,124 +5008,124 @@
       </c>
       <c r="B6" s="8" t="inlineStr">
         <is>
-          <t>Aluguel</t>
+          <t>Sistemas e contabilidade</t>
         </is>
       </c>
       <c r="C6" s="8" t="inlineStr">
         <is>
-          <t>Aluguel do imóvel</t>
+          <t>Sistema de automação e contabilidade</t>
         </is>
       </c>
       <c r="D6" s="16" t="n">
-        <v>38000</v>
+        <v>4300</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="12" t="n">
-        <v>45940</v>
+        <v>45942</v>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Sistemas e contabilidade</t>
+          <t>Taxas de cartão</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Sistema de automação e contabilidade</t>
+          <t>Taxas das maquininhas (semana)</t>
         </is>
       </c>
       <c r="D7" s="17" t="n">
-        <v>4300</v>
+        <v>5678.61</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="7" t="n">
-        <v>45941</v>
+        <v>45942</v>
       </c>
       <c r="B8" s="8" t="inlineStr">
         <is>
-          <t>Manutenção</t>
+          <t>Água e esgoto</t>
         </is>
       </c>
       <c r="C8" s="8" t="inlineStr">
         <is>
-          <t>Reparo elétrico</t>
+          <t>Conta de água</t>
         </is>
       </c>
       <c r="D8" s="16" t="n">
-        <v>5561.51</v>
+        <v>1785.53</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="12" t="n">
-        <v>45942</v>
+        <v>45945</v>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Taxas de cartão</t>
+          <t>Energia elétrica</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Taxas das maquininhas (semana)</t>
+          <t>Conta de energia</t>
         </is>
       </c>
       <c r="D9" s="17" t="n">
-        <v>5367.92</v>
+        <v>13118.76</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="7" t="n">
-        <v>45942</v>
+        <v>45945</v>
       </c>
       <c r="B10" s="8" t="inlineStr">
         <is>
-          <t>Água e esgoto</t>
+          <t>Marketing</t>
         </is>
       </c>
       <c r="C10" s="8" t="inlineStr">
         <is>
-          <t>Conta de água</t>
+          <t>Placas, redes sociais e brindes</t>
         </is>
       </c>
       <c r="D10" s="16" t="n">
-        <v>1834.46</v>
+        <v>3640.72</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="12" t="n">
-        <v>45945</v>
+        <v>45946</v>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Energia elétrica</t>
+          <t>Manutenção</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Conta de energia</t>
+          <t>Troca de filtros das bombas</t>
         </is>
       </c>
       <c r="D11" s="17" t="n">
-        <v>13407.29</v>
+        <v>4079.94</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="7" t="n">
-        <v>45945</v>
+        <v>45949</v>
       </c>
       <c r="B12" s="8" t="inlineStr">
         <is>
-          <t>Marketing</t>
+          <t>Outras despesas</t>
         </is>
       </c>
       <c r="C12" s="8" t="inlineStr">
         <is>
-          <t>Placas, redes sociais e brindes</t>
+          <t>Monitoramento e alarme</t>
         </is>
       </c>
       <c r="D12" s="16" t="n">
-        <v>4771.87</v>
+        <v>2358.39</v>
       </c>
     </row>
     <row r="13">
@@ -5143,7 +5143,7 @@
         </is>
       </c>
       <c r="D13" s="17" t="n">
-        <v>5459.15</v>
+        <v>5805.12</v>
       </c>
     </row>
     <row r="14">
@@ -5161,12 +5161,12 @@
         </is>
       </c>
       <c r="D14" s="16" t="n">
-        <v>27803.08</v>
+        <v>27788.02</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="12" t="n">
-        <v>45951</v>
+        <v>45950</v>
       </c>
       <c r="B15" t="inlineStr">
         <is>
@@ -5175,16 +5175,16 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Coleta de resíduos (óleo e borra)</t>
+          <t>Tarifas bancárias</t>
         </is>
       </c>
       <c r="D15" s="17" t="n">
-        <v>1576.92</v>
+        <v>1081.03</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="7" t="n">
-        <v>45955</v>
+        <v>45951</v>
       </c>
       <c r="B16" s="8" t="inlineStr">
         <is>
@@ -5193,11 +5193,11 @@
       </c>
       <c r="C16" s="8" t="inlineStr">
         <is>
-          <t>Manutenção do compressor de ar</t>
+          <t>Manutenção preventiva das bombas</t>
         </is>
       </c>
       <c r="D16" s="16" t="n">
-        <v>2850.77</v>
+        <v>4103.52</v>
       </c>
     </row>
     <row r="17">
@@ -5215,7 +5215,7 @@
         </is>
       </c>
       <c r="D17" s="17" t="n">
-        <v>5910.95</v>
+        <v>5571.3</v>
       </c>
     </row>
     <row r="18">
@@ -5233,7 +5233,7 @@
         </is>
       </c>
       <c r="D18" s="16" t="n">
-        <v>4166.08</v>
+        <v>4123.2</v>
       </c>
     </row>
   </sheetData>
